--- a/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 23.xlsx
+++ b/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 23.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Exel Admin Keuangan 23\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Keuangan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E89E2573-A086-40BA-8BDD-AC56810CDCC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="0" windowWidth="20310" windowHeight="10920" xr2:uid="{417758A1-4307-4B61-947F-57E7975BA7C9}"/>
+    <workbookView xWindow="180" yWindow="0" windowWidth="20310" windowHeight="10920"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -204,7 +203,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -711,7 +710,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61D12291-72CC-44E0-852E-4A75FE2421CF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -791,13 +790,34 @@
       <c r="D3" s="6">
         <v>45108</v>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="12"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="11"/>
+      <c r="E3" s="11" t="str">
+        <f>VLOOKUP(LEFT(B3,4),$B$10:$D$13,2,FALSE)</f>
+        <v>SBY-JAKARTA</v>
+      </c>
+      <c r="F3" s="12">
+        <f>VLOOKUP(LEFT(B3,4),$B$10:$D$13,3,FALSE)</f>
+        <v>750000</v>
+      </c>
+      <c r="G3" s="11" t="str">
+        <f>VLOOKUP(MID(B3,6,1),$B$15:$D$18,2,FALSE)</f>
+        <v>EKONOMI</v>
+      </c>
+      <c r="H3" s="13" t="str">
+        <f>HLOOKUP(MID(B3,8,2),$B$20:$E$22,2,FALSE)</f>
+        <v>PAKET 1</v>
+      </c>
+      <c r="I3" s="12">
+        <f>HLOOKUP(H3,$C$21:$E$22,2,FALSE)</f>
+        <v>40000</v>
+      </c>
+      <c r="J3" s="11">
+        <f>VLOOKUP(MID(B3,6,1),$B$15:$D$18,3,FALSE)*F3</f>
+        <v>0</v>
+      </c>
+      <c r="K3" s="11">
+        <f>F3+I3+J3</f>
+        <v>790000</v>
+      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
@@ -812,13 +832,34 @@
       <c r="D4" s="6">
         <v>45108</v>
       </c>
-      <c r="E4" s="11"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="11"/>
+      <c r="E4" s="11" t="str">
+        <f t="shared" ref="E4:E8" si="0">VLOOKUP(LEFT(B4,4),$B$10:$D$13,2,FALSE)</f>
+        <v>SBY-JAKARTA</v>
+      </c>
+      <c r="F4" s="12">
+        <f t="shared" ref="F4:F8" si="1">VLOOKUP(LEFT(B4,4),$B$10:$D$13,3,FALSE)</f>
+        <v>750000</v>
+      </c>
+      <c r="G4" s="11" t="str">
+        <f t="shared" ref="G4:G8" si="2">VLOOKUP(MID(B4,6,1),$B$15:$D$18,2,FALSE)</f>
+        <v>BISNIS</v>
+      </c>
+      <c r="H4" s="13" t="str">
+        <f t="shared" ref="H4:H8" si="3">HLOOKUP(MID(B4,8,2),$B$20:$E$22,2,FALSE)</f>
+        <v>PAKET 2</v>
+      </c>
+      <c r="I4" s="12">
+        <f t="shared" ref="I4:I8" si="4">HLOOKUP(H4,$C$21:$E$22,2,FALSE)</f>
+        <v>60000</v>
+      </c>
+      <c r="J4" s="11">
+        <f t="shared" ref="J4:J8" si="5">VLOOKUP(MID(B4,6,1),$B$15:$D$18,3,FALSE)*F4</f>
+        <v>112500</v>
+      </c>
+      <c r="K4" s="11">
+        <f t="shared" ref="K4:K8" si="6">F4+I4+J4</f>
+        <v>922500</v>
+      </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
@@ -833,13 +874,34 @@
       <c r="D5" s="6">
         <v>45112</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="11"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="11"/>
+      <c r="E5" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>SBY-JAKARTA</v>
+      </c>
+      <c r="F5" s="12">
+        <f t="shared" si="1"/>
+        <v>750000</v>
+      </c>
+      <c r="G5" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v>EKONOMI</v>
+      </c>
+      <c r="H5" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>PAKET 1</v>
+      </c>
+      <c r="I5" s="12">
+        <f t="shared" si="4"/>
+        <v>40000</v>
+      </c>
+      <c r="J5" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K5" s="11">
+        <f t="shared" si="6"/>
+        <v>790000</v>
+      </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
@@ -854,13 +916,34 @@
       <c r="D6" s="6">
         <v>45112</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="11"/>
+      <c r="E6" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>SBY-BALI</v>
+      </c>
+      <c r="F6" s="12">
+        <f t="shared" si="1"/>
+        <v>850000</v>
+      </c>
+      <c r="G6" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v>EKONOMI</v>
+      </c>
+      <c r="H6" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>PAKET 1</v>
+      </c>
+      <c r="I6" s="12">
+        <f t="shared" si="4"/>
+        <v>40000</v>
+      </c>
+      <c r="J6" s="11">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K6" s="11">
+        <f t="shared" si="6"/>
+        <v>890000</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
@@ -875,13 +958,34 @@
       <c r="D7" s="6">
         <v>45117</v>
       </c>
-      <c r="E7" s="11"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="12"/>
-      <c r="J7" s="13"/>
-      <c r="K7" s="11"/>
+      <c r="E7" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>SBY-BALI</v>
+      </c>
+      <c r="F7" s="12">
+        <f t="shared" si="1"/>
+        <v>850000</v>
+      </c>
+      <c r="G7" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v>FIRST CLASS</v>
+      </c>
+      <c r="H7" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>PAKET 3</v>
+      </c>
+      <c r="I7" s="12">
+        <f t="shared" si="4"/>
+        <v>80000</v>
+      </c>
+      <c r="J7" s="11">
+        <f t="shared" si="5"/>
+        <v>212500</v>
+      </c>
+      <c r="K7" s="11">
+        <f t="shared" si="6"/>
+        <v>1142500</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
@@ -896,13 +1000,34 @@
       <c r="D8" s="6">
         <v>45118</v>
       </c>
-      <c r="E8" s="11"/>
-      <c r="F8" s="12"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="12"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="11"/>
+      <c r="E8" s="11" t="str">
+        <f t="shared" si="0"/>
+        <v>SBY-JOGJA</v>
+      </c>
+      <c r="F8" s="12">
+        <f t="shared" si="1"/>
+        <v>800000</v>
+      </c>
+      <c r="G8" s="11" t="str">
+        <f t="shared" si="2"/>
+        <v>FIRST CLASS</v>
+      </c>
+      <c r="H8" s="13" t="str">
+        <f t="shared" si="3"/>
+        <v>PAKET 3</v>
+      </c>
+      <c r="I8" s="12">
+        <f t="shared" si="4"/>
+        <v>80000</v>
+      </c>
+      <c r="J8" s="11">
+        <f t="shared" si="5"/>
+        <v>200000</v>
+      </c>
+      <c r="K8" s="11">
+        <f t="shared" si="6"/>
+        <v>1080000</v>
+      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H9" s="18" t="s">
@@ -910,7 +1035,10 @@
       </c>
       <c r="I9" s="18"/>
       <c r="J9" s="18"/>
-      <c r="K9" s="11"/>
+      <c r="K9" s="11">
+        <f>SUM(K3:K8)</f>
+        <v>5615000</v>
+      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
@@ -931,7 +1059,10 @@
       </c>
       <c r="I10" s="18"/>
       <c r="J10" s="18"/>
-      <c r="K10" s="14"/>
+      <c r="K10" s="14">
+        <f>SUMIF(G3:G8,"EKONOMI",K3:K8)</f>
+        <v>2470000</v>
+      </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
@@ -952,7 +1083,10 @@
       </c>
       <c r="I11" s="18"/>
       <c r="J11" s="18"/>
-      <c r="K11" s="14"/>
+      <c r="K11" s="14">
+        <f>SUMIF(G4:G9,"BISNIS",K4:K9)</f>
+        <v>922500</v>
+      </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -969,7 +1103,10 @@
       </c>
       <c r="I12" s="18"/>
       <c r="J12" s="18"/>
-      <c r="K12" s="14"/>
+      <c r="K12" s="14">
+        <f>SUMIF(G5:G10,"FIRST CLASS",K5:K10)</f>
+        <v>2222500</v>
+      </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
@@ -1123,7 +1260,7 @@
     <mergeCell ref="E11:F11"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E11" r:id="rId1" xr:uid="{44063B3F-7C33-4026-A005-47488D186CC5}"/>
+    <hyperlink ref="E11" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 23.xlsx
+++ b/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 23.xlsx
@@ -1,23 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Keuangan\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5400A27D-813A-4E51-A8E1-254946966CAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="180" yWindow="0" windowWidth="20310" windowHeight="10920"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{417758A1-4307-4B61-947F-57E7975BA7C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -203,7 +213,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
@@ -710,7 +720,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61D12291-72CC-44E0-852E-4A75FE2421CF}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -794,7 +804,7 @@
         <f>VLOOKUP(LEFT(B3,4),$B$10:$D$13,2,FALSE)</f>
         <v>SBY-JAKARTA</v>
       </c>
-      <c r="F3" s="12">
+      <c r="F3" s="11">
         <f>VLOOKUP(LEFT(B3,4),$B$10:$D$13,3,FALSE)</f>
         <v>750000</v>
       </c>
@@ -802,22 +812,10 @@
         <f>VLOOKUP(MID(B3,6,1),$B$15:$D$18,2,FALSE)</f>
         <v>EKONOMI</v>
       </c>
-      <c r="H3" s="13" t="str">
-        <f>HLOOKUP(MID(B3,8,2),$B$20:$E$22,2,FALSE)</f>
-        <v>PAKET 1</v>
-      </c>
-      <c r="I3" s="12">
-        <f>HLOOKUP(H3,$C$21:$E$22,2,FALSE)</f>
-        <v>40000</v>
-      </c>
-      <c r="J3" s="11">
-        <f>VLOOKUP(MID(B3,6,1),$B$15:$D$18,3,FALSE)*F3</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="11">
-        <f>F3+I3+J3</f>
-        <v>790000</v>
-      </c>
+      <c r="H3" s="13"/>
+      <c r="I3" s="12"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="11"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="4">
@@ -833,10 +831,10 @@
         <v>45108</v>
       </c>
       <c r="E4" s="11" t="str">
-        <f t="shared" ref="E4:E8" si="0">VLOOKUP(LEFT(B4,4),$B$10:$D$13,2,FALSE)</f>
+        <f t="shared" ref="E4:F8" si="0">VLOOKUP(LEFT(B4,4),$B$10:$D$13,2,FALSE)</f>
         <v>SBY-JAKARTA</v>
       </c>
-      <c r="F4" s="12">
+      <c r="F4" s="11">
         <f t="shared" ref="F4:F8" si="1">VLOOKUP(LEFT(B4,4),$B$10:$D$13,3,FALSE)</f>
         <v>750000</v>
       </c>
@@ -844,22 +842,10 @@
         <f t="shared" ref="G4:G8" si="2">VLOOKUP(MID(B4,6,1),$B$15:$D$18,2,FALSE)</f>
         <v>BISNIS</v>
       </c>
-      <c r="H4" s="13" t="str">
-        <f t="shared" ref="H4:H8" si="3">HLOOKUP(MID(B4,8,2),$B$20:$E$22,2,FALSE)</f>
-        <v>PAKET 2</v>
-      </c>
-      <c r="I4" s="12">
-        <f t="shared" ref="I4:I8" si="4">HLOOKUP(H4,$C$21:$E$22,2,FALSE)</f>
-        <v>60000</v>
-      </c>
-      <c r="J4" s="11">
-        <f t="shared" ref="J4:J8" si="5">VLOOKUP(MID(B4,6,1),$B$15:$D$18,3,FALSE)*F4</f>
-        <v>112500</v>
-      </c>
-      <c r="K4" s="11">
-        <f t="shared" ref="K4:K8" si="6">F4+I4+J4</f>
-        <v>922500</v>
-      </c>
+      <c r="H4" s="13"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="11"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="4">
@@ -878,7 +864,7 @@
         <f t="shared" si="0"/>
         <v>SBY-JAKARTA</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="11">
         <f t="shared" si="1"/>
         <v>750000</v>
       </c>
@@ -886,22 +872,10 @@
         <f t="shared" si="2"/>
         <v>EKONOMI</v>
       </c>
-      <c r="H5" s="13" t="str">
-        <f t="shared" si="3"/>
-        <v>PAKET 1</v>
-      </c>
-      <c r="I5" s="12">
-        <f t="shared" si="4"/>
-        <v>40000</v>
-      </c>
-      <c r="J5" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K5" s="11">
-        <f t="shared" si="6"/>
-        <v>790000</v>
-      </c>
+      <c r="H5" s="13"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="11"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="4">
@@ -920,7 +894,7 @@
         <f t="shared" si="0"/>
         <v>SBY-BALI</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="11">
         <f t="shared" si="1"/>
         <v>850000</v>
       </c>
@@ -928,22 +902,10 @@
         <f t="shared" si="2"/>
         <v>EKONOMI</v>
       </c>
-      <c r="H6" s="13" t="str">
-        <f t="shared" si="3"/>
-        <v>PAKET 1</v>
-      </c>
-      <c r="I6" s="12">
-        <f t="shared" si="4"/>
-        <v>40000</v>
-      </c>
-      <c r="J6" s="11">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K6" s="11">
-        <f t="shared" si="6"/>
-        <v>890000</v>
-      </c>
+      <c r="H6" s="13"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="11"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4">
@@ -962,7 +924,7 @@
         <f t="shared" si="0"/>
         <v>SBY-BALI</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="11">
         <f t="shared" si="1"/>
         <v>850000</v>
       </c>
@@ -970,22 +932,10 @@
         <f t="shared" si="2"/>
         <v>FIRST CLASS</v>
       </c>
-      <c r="H7" s="13" t="str">
-        <f t="shared" si="3"/>
-        <v>PAKET 3</v>
-      </c>
-      <c r="I7" s="12">
-        <f t="shared" si="4"/>
-        <v>80000</v>
-      </c>
-      <c r="J7" s="11">
-        <f t="shared" si="5"/>
-        <v>212500</v>
-      </c>
-      <c r="K7" s="11">
-        <f t="shared" si="6"/>
-        <v>1142500</v>
-      </c>
+      <c r="H7" s="13"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="11"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="4">
@@ -1004,7 +954,7 @@
         <f t="shared" si="0"/>
         <v>SBY-JOGJA</v>
       </c>
-      <c r="F8" s="12">
+      <c r="F8" s="11">
         <f t="shared" si="1"/>
         <v>800000</v>
       </c>
@@ -1012,22 +962,10 @@
         <f t="shared" si="2"/>
         <v>FIRST CLASS</v>
       </c>
-      <c r="H8" s="13" t="str">
-        <f t="shared" si="3"/>
-        <v>PAKET 3</v>
-      </c>
-      <c r="I8" s="12">
-        <f t="shared" si="4"/>
-        <v>80000</v>
-      </c>
-      <c r="J8" s="11">
-        <f t="shared" si="5"/>
-        <v>200000</v>
-      </c>
-      <c r="K8" s="11">
-        <f t="shared" si="6"/>
-        <v>1080000</v>
-      </c>
+      <c r="H8" s="13"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="11"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="H9" s="18" t="s">
@@ -1035,10 +973,7 @@
       </c>
       <c r="I9" s="18"/>
       <c r="J9" s="18"/>
-      <c r="K9" s="11">
-        <f>SUM(K3:K8)</f>
-        <v>5615000</v>
-      </c>
+      <c r="K9" s="11"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B10" s="8" t="s">
@@ -1059,10 +994,7 @@
       </c>
       <c r="I10" s="18"/>
       <c r="J10" s="18"/>
-      <c r="K10" s="14">
-        <f>SUMIF(G3:G8,"EKONOMI",K3:K8)</f>
-        <v>2470000</v>
-      </c>
+      <c r="K10" s="14"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
@@ -1083,10 +1015,7 @@
       </c>
       <c r="I11" s="18"/>
       <c r="J11" s="18"/>
-      <c r="K11" s="14">
-        <f>SUMIF(G4:G9,"BISNIS",K4:K9)</f>
-        <v>922500</v>
-      </c>
+      <c r="K11" s="14"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
@@ -1103,10 +1032,7 @@
       </c>
       <c r="I12" s="18"/>
       <c r="J12" s="18"/>
-      <c r="K12" s="14">
-        <f>SUMIF(G5:G10,"FIRST CLASS",K5:K10)</f>
-        <v>2222500</v>
-      </c>
+      <c r="K12" s="14"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
@@ -1260,7 +1186,7 @@
     <mergeCell ref="E11:F11"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="E11" r:id="rId1"/>
+    <hyperlink ref="E11" r:id="rId1" xr:uid="{44063B3F-7C33-4026-A005-47488D186CC5}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
